--- a/plots/livlipid_betaglm_table.xlsx
+++ b/plots/livlipid_betaglm_table.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="61">
   <si>
     <t>common_name</t>
   </si>
@@ -95,15 +95,12 @@
     <t>14.3</t>
   </si>
   <si>
-    <t>13.9</t>
+    <t>13.3</t>
   </si>
   <si>
     <t>15.2</t>
   </si>
   <si>
-    <t>13.3</t>
-  </si>
-  <si>
     <t>13.1</t>
   </si>
   <si>
@@ -119,7 +116,7 @@
     <t>42.6</t>
   </si>
   <si>
-    <t>45.5</t>
+    <t>43.7</t>
   </si>
   <si>
     <t>50.4</t>
@@ -131,7 +128,7 @@
     <t>44.8</t>
   </si>
   <si>
-    <t>61.4</t>
+    <t>61.8</t>
   </si>
   <si>
     <t>71.8</t>
@@ -143,7 +140,7 @@
     <t>10.3</t>
   </si>
   <si>
-    <t>10.8</t>
+    <t>10.2</t>
   </si>
   <si>
     <t>11.3</t>
@@ -152,7 +149,7 @@
     <t xml:space="preserve"> 9.8</t>
   </si>
   <si>
-    <t>13.6</t>
+    <t>13.7</t>
   </si>
   <si>
     <t>14.6</t>
@@ -164,7 +161,7 @@
     <t>0.28</t>
   </si>
   <si>
-    <t>0.30</t>
+    <t>0.36</t>
   </si>
   <si>
     <t>0.17</t>
@@ -185,7 +182,7 @@
     <t>-0.008</t>
   </si>
   <si>
-    <t xml:space="preserve"> 0.005</t>
+    <t>-0.001</t>
   </si>
   <si>
     <t>-0.010</t>
@@ -303,16 +300,16 @@
         <v>25</v>
       </c>
       <c r="H2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3">
@@ -338,16 +335,16 @@
         <v>26</v>
       </c>
       <c r="H3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
@@ -364,25 +361,25 @@
         <v>23</v>
       </c>
       <c r="E4" t="n">
-        <v>-92.01</v>
+        <v>-87.65</v>
       </c>
       <c r="F4" t="n">
-        <v>34.95</v>
+        <v>39.31</v>
       </c>
       <c r="G4" t="s">
         <v>27</v>
       </c>
       <c r="H4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5">
@@ -408,16 +405,16 @@
         <v>28</v>
       </c>
       <c r="H5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6">
@@ -440,19 +437,19 @@
         <v>0.0</v>
       </c>
       <c r="G6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7">
@@ -475,19 +472,19 @@
         <v>26.28</v>
       </c>
       <c r="G7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8">
@@ -504,25 +501,25 @@
         <v>24</v>
       </c>
       <c r="E8" t="n">
-        <v>-74.99</v>
+        <v>-74.14</v>
       </c>
       <c r="F8" t="n">
-        <v>60.04</v>
+        <v>60.89</v>
       </c>
       <c r="G8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9">
@@ -545,19 +542,19 @@
         <v>71.19</v>
       </c>
       <c r="G9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/plots/livlipid_betaglm_table.xlsx
+++ b/plots/livlipid_betaglm_table.xlsx
@@ -128,7 +128,7 @@
     <t>44.8</t>
   </si>
   <si>
-    <t>61.8</t>
+    <t>61.9</t>
   </si>
   <si>
     <t>71.8</t>
@@ -361,10 +361,10 @@
         <v>23</v>
       </c>
       <c r="E4" t="n">
-        <v>-87.65</v>
+        <v>-87.72</v>
       </c>
       <c r="F4" t="n">
-        <v>39.31</v>
+        <v>39.24</v>
       </c>
       <c r="G4" t="s">
         <v>27</v>
@@ -501,10 +501,10 @@
         <v>24</v>
       </c>
       <c r="E8" t="n">
-        <v>-74.14</v>
+        <v>-73.98</v>
       </c>
       <c r="F8" t="n">
-        <v>60.89</v>
+        <v>61.05</v>
       </c>
       <c r="G8" t="s">
         <v>30</v>

--- a/plots/livlipid_betaglm_table.xlsx
+++ b/plots/livlipid_betaglm_table.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="71">
   <si>
     <t>common_name</t>
   </si>
@@ -65,7 +65,10 @@
     <t>Null</t>
   </si>
   <si>
-    <t>P_LIVLIPID ~ poly(HSI_PCT, 3) + (1 | UNIQUE_HAUL) + (1 | YEAR_FAC) +     (0 + LENGTH_CM | SPECIES)</t>
+    <t>FT-NIR</t>
+  </si>
+  <si>
+    <t>P_LIVLIPID ~ poly(HSI_PCT, 2) + (1 | UNIQUE_HAUL) + (1 | YEAR_FAC) +     (0 + LENGTH_CM | SPECIES)</t>
   </si>
   <si>
     <t>P_LIVLIPID ~ poly(DISTELL_LIVER, 1) + (1 | UNIQUE_HAUL) + (1 |     YEAR_FAC) + (0 + LENGTH_CM | SPECIES)</t>
@@ -77,124 +80,151 @@
     <t>P_LIVLIPID ~ 1 + (1 | UNIQUE_HAUL) + (1 | YEAR_FAC) + (0 + LENGTH_CM |     SPECIES)</t>
   </si>
   <si>
-    <t>P_LIVLIPID ~ poly(HSI_PCT, 2) + (1 | UNIQUE_HAUL) + (1 | YEAR_FAC) +     (0 + LENGTH_CM | SPECIES)</t>
-  </si>
-  <si>
-    <t>P_LIVLIPID ~ poly(LOG_LW_RESID, 2) + (1 | UNIQUE_HAUL) + (1 |     YEAR_FAC) + (0 + LENGTH_CM | SPECIES)</t>
-  </si>
-  <si>
     <t>~log(LENGTH_CM)</t>
   </si>
   <si>
     <t>~1</t>
   </si>
   <si>
-    <t>11.5</t>
-  </si>
-  <si>
-    <t>14.3</t>
+    <t>10.6</t>
+  </si>
+  <si>
+    <t>13.5</t>
+  </si>
+  <si>
+    <t>12.8</t>
+  </si>
+  <si>
+    <t>14.4</t>
+  </si>
+  <si>
+    <t>11.3</t>
+  </si>
+  <si>
+    <t>12.4</t>
+  </si>
+  <si>
+    <t>15.1</t>
+  </si>
+  <si>
+    <t>15.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 8.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7.5</t>
+  </si>
+  <si>
+    <t>20.2</t>
+  </si>
+  <si>
+    <t>25.0</t>
+  </si>
+  <si>
+    <t>26.3</t>
+  </si>
+  <si>
+    <t>29.6</t>
+  </si>
+  <si>
+    <t>25.2</t>
+  </si>
+  <si>
+    <t>29.8</t>
+  </si>
+  <si>
+    <t>38.7</t>
+  </si>
+  <si>
+    <t>42.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 9.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 9.9</t>
+  </si>
+  <si>
+    <t>10.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 8.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 9.6</t>
+  </si>
+  <si>
+    <t>12.5</t>
   </si>
   <si>
     <t>13.3</t>
   </si>
   <si>
-    <t>15.2</t>
-  </si>
-  <si>
-    <t>13.1</t>
-  </si>
-  <si>
-    <t>16.2</t>
-  </si>
-  <si>
-    <t>17.1</t>
-  </si>
-  <si>
-    <t>29.5</t>
-  </si>
-  <si>
-    <t>42.6</t>
-  </si>
-  <si>
-    <t>43.7</t>
-  </si>
-  <si>
-    <t>50.4</t>
-  </si>
-  <si>
-    <t>51.2</t>
-  </si>
-  <si>
-    <t>44.8</t>
-  </si>
-  <si>
-    <t>61.9</t>
-  </si>
-  <si>
-    <t>71.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 8.6</t>
-  </si>
-  <si>
-    <t>10.3</t>
-  </si>
-  <si>
-    <t>10.2</t>
-  </si>
-  <si>
-    <t>11.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 9.8</t>
-  </si>
-  <si>
-    <t>13.7</t>
-  </si>
-  <si>
-    <t>14.6</t>
-  </si>
-  <si>
-    <t>0.53</t>
-  </si>
-  <si>
-    <t>0.28</t>
-  </si>
-  <si>
-    <t>0.36</t>
-  </si>
-  <si>
-    <t>0.17</t>
-  </si>
-  <si>
-    <t>0.45</t>
-  </si>
-  <si>
-    <t>0.16</t>
-  </si>
-  <si>
-    <t>0.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.008</t>
-  </si>
-  <si>
-    <t>-0.008</t>
+    <t xml:space="preserve"> 6.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 5.6</t>
+  </si>
+  <si>
+    <t>0.51</t>
+  </si>
+  <si>
+    <t>0.23</t>
+  </si>
+  <si>
+    <t>0.29</t>
+  </si>
+  <si>
+    <t>0.09</t>
+  </si>
+  <si>
+    <t>0.47</t>
+  </si>
+  <si>
+    <t>0.32</t>
+  </si>
+  <si>
+    <t>0.03</t>
+  </si>
+  <si>
+    <t>0.08</t>
+  </si>
+  <si>
+    <t>0.71</t>
+  </si>
+  <si>
+    <t>0.74</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.003</t>
+  </si>
+  <si>
+    <t>-0.004</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.000</t>
+  </si>
+  <si>
+    <t>-0.005</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.017</t>
   </si>
   <si>
     <t>-0.001</t>
   </si>
   <si>
-    <t>-0.010</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.024</t>
-  </si>
-  <si>
-    <t>-0.003</t>
-  </si>
-  <si>
-    <t>-0.006</t>
+    <t>-0.002</t>
   </si>
 </sst>
 </file>
@@ -285,31 +315,31 @@
         <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E2" t="n">
-        <v>-126.96</v>
+        <v>-116.51</v>
       </c>
       <c r="F2" t="n">
         <v>0.0</v>
       </c>
       <c r="G2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="J2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="K2" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3">
@@ -320,31 +350,31 @@
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E3" t="n">
-        <v>-98.99</v>
+        <v>-114.27</v>
       </c>
       <c r="F3" t="n">
-        <v>27.97</v>
+        <v>2.24000000000001</v>
       </c>
       <c r="G3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="K3" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4">
@@ -355,31 +385,31 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E4" t="n">
-        <v>-87.72</v>
+        <v>-86.82</v>
       </c>
       <c r="F4" t="n">
-        <v>39.24</v>
+        <v>29.69</v>
       </c>
       <c r="G4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J4" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="K4" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5">
@@ -390,31 +420,31 @@
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E5" t="n">
-        <v>-57.75</v>
+        <v>-66.65</v>
       </c>
       <c r="F5" t="n">
-        <v>69.21</v>
+        <v>49.86</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I5" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J5" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="K5" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6">
@@ -425,31 +455,31 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E6" t="n">
-        <v>-135.03</v>
+        <v>-120.55</v>
       </c>
       <c r="F6" t="n">
         <v>0.0</v>
       </c>
       <c r="G6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I6" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J6" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="K6" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7">
@@ -460,31 +490,31 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E7" t="n">
-        <v>-108.75</v>
+        <v>-89.97</v>
       </c>
       <c r="F7" t="n">
-        <v>26.28</v>
+        <v>30.58</v>
       </c>
       <c r="G7" t="s">
         <v>29</v>
       </c>
       <c r="H7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I7" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="J7" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="K7" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8">
@@ -495,31 +525,31 @@
         <v>15</v>
       </c>
       <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
         <v>22</v>
       </c>
-      <c r="D8" t="s">
-        <v>24</v>
-      </c>
       <c r="E8" t="n">
-        <v>-73.98</v>
+        <v>-68.85</v>
       </c>
       <c r="F8" t="n">
-        <v>61.05</v>
+        <v>51.7</v>
       </c>
       <c r="G8" t="s">
         <v>30</v>
       </c>
       <c r="H8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I8" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J8" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="K8" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9">
@@ -530,31 +560,101 @@
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E9" t="n">
-        <v>-63.84</v>
+        <v>-68.52</v>
       </c>
       <c r="F9" t="n">
-        <v>71.19</v>
+        <v>52.03</v>
       </c>
       <c r="G9" t="s">
         <v>31</v>
       </c>
       <c r="H9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I9" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="J9" t="s">
+        <v>61</v>
+      </c>
+      <c r="K9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G10" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" t="s">
+        <v>42</v>
+      </c>
+      <c r="I10" t="s">
+        <v>52</v>
+      </c>
+      <c r="J10" t="s">
+        <v>62</v>
+      </c>
+      <c r="K10" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G11" t="s">
+        <v>33</v>
+      </c>
+      <c r="H11" t="s">
+        <v>43</v>
+      </c>
+      <c r="I11" t="s">
         <v>53</v>
       </c>
-      <c r="K9" t="s">
-        <v>60</v>
+      <c r="J11" t="s">
+        <v>63</v>
+      </c>
+      <c r="K11" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/plots/livlipid_betaglm_table.xlsx
+++ b/plots/livlipid_betaglm_table.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="72">
   <si>
     <t>common_name</t>
   </si>
@@ -113,7 +113,7 @@
     <t xml:space="preserve"> 8.2</t>
   </si>
   <si>
-    <t xml:space="preserve"> 7.5</t>
+    <t xml:space="preserve"> 8.5</t>
   </si>
   <si>
     <t>20.2</t>
@@ -140,10 +140,10 @@
     <t>42.9</t>
   </si>
   <si>
-    <t xml:space="preserve"> 0.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.1</t>
+    <t>18.5</t>
+  </si>
+  <si>
+    <t>14.9</t>
   </si>
   <si>
     <t xml:space="preserve"> 7.9</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve"> 6.7</t>
   </si>
   <si>
-    <t xml:space="preserve"> 5.6</t>
+    <t xml:space="preserve"> 6.2</t>
   </si>
   <si>
     <t>0.51</t>
@@ -203,7 +203,7 @@
     <t>0.71</t>
   </si>
   <si>
-    <t>0.74</t>
+    <t>0.69</t>
   </si>
   <si>
     <t xml:space="preserve"> 0.003</t>
@@ -225,6 +225,9 @@
   </si>
   <si>
     <t>-0.002</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.005</t>
   </si>
 </sst>
 </file>
@@ -654,7 +657,7 @@
         <v>63</v>
       </c>
       <c r="K11" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
